--- a/apps/dashboard-selector/Cool_Hollow_Coaching_Milestone_3_Dashboard_Template.xlsx
+++ b/apps/dashboard-selector/Cool_Hollow_Coaching_Milestone_3_Dashboard_Template.xlsx
@@ -35,17 +35,17 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00E8C766"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
     <font>
@@ -56,7 +56,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -74,11 +74,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <i val="1"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -87,12 +87,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E4643"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00589BA8"/>
+        <fgColor rgb="001A1A1A"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,12 +97,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B4D351"/>
+        <fgColor rgb="00E8C766"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAF8F3"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -149,19 +144,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>

--- a/apps/dashboard-selector/Cool_Hollow_Coaching_Milestone_3_Dashboard_Template.xlsx
+++ b/apps/dashboard-selector/Cool_Hollow_Coaching_Milestone_3_Dashboard_Template.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Candidate Metrics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Examples" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Starter Ideas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Candidate Metrics" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="10">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,12 +43,32 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="001A1A1A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="005A5A5A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
@@ -61,21 +85,8 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="005A5A5A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
       <color rgb="006B6B6B"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color rgb="001A1A1A"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -92,12 +103,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEFEF"/>
+        <fgColor rgb="00E8C766"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8C766"/>
+        <fgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
     <fill>
@@ -132,11 +143,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -144,19 +156,30 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -519,10 +542,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001A1A1A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -535,137 +559,156 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 3: The Monday Morning Dashboard</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>How to use this template</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>List every metric you could track across cash, sales, delivery, customer, and team. Add as many candidates per category as you like. The tool picks the single best one per category and builds your five-metric dashboard.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="6" ht="68" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>List every metric you could track across cash, sales, delivery, customer, and team. Add as many candidates per category as you like. The tool picks the single best one per category and builds your five-metric dashboard. The Starter Ideas tab lists proven candidates for each category if you're not sure what to consider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Three steps: fill in the data tab(s), save this file, then upload this same file into the tool. The Examples and Starter Ideas tabs are for reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads them, only type your real data on the data tab(s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>On the "Candidate Metrics" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>What to put here</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>cash, sales, delivery, customer, or team. One winning metric gets picked per category.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>cash, sales, delivery, customer, or team. One winning metric gets picked per category, so add candidates to all five.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Metric Name</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>What this metric is called, in plain English.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Current Value</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Where this metric stands today, as a number.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Target Value</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Where you want this metric to be.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>higher_better if more is good, lower_better if less is good.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Leading</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>yes or no. Does this metric move before a problem shows up elsewhere?</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>1 to 5. How directly this metric reflects whether the business is actually healthy.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Fill in the data tab, save the file, then upload it straight into the tool.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -674,10 +717,444 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="006B6B6B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cool Hollow Coaching · Business Without You</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Milestone 3: The Monday Morning Dashboard</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Filled-in examples, for reference only. Type your own data on the data tab(s), not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads this tab, anything you type here is ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Example for the "Candidate Metrics" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Metric Name</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Current Value</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Target Value</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Leading</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>13-week cash runway (weeks)</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>higher_better</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Monthly revenue</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>42000</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>higher_better</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Net promoter score</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>higher_better</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00E8C766"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cool Hollow Coaching · Business Without You</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Milestone 3: The Monday Morning Dashboard</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>The most common answers we see across owner-run businesses. Copy any that are true for yours onto the data tab, reworded to match how your business actually runs, then fill in the numbers and ratings yourself, honestly. Don't copy anything that isn't real for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads this tab, copy items onto the data tab to use them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Weeks of cash runway</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Days customers take to pay (AR days)</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Cash balance vs next payroll due</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Monthly revenue</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Quotes or proposals sent per week</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Close rate on quotes</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Average job or order value</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>On-time completion rate</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Jobs or orders completed per week</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Rework or callback rate</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Complaints per week</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Repeat purchase rate</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>New reviews per month (and average rating)</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Open roles unfilled</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>Overtime hours per week</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>Staff turnover in the last 90 days</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A22:B22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C8A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -695,453 +1172,440 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 3: The Monday Morning Dashboard</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Metric Name</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Current Value</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Target Value</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Leading</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>13-week cash runway (weeks)</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>higher_better</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="17" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Monthly revenue</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>42000</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>higher_better</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Your data starts here, replace or delete the example rows above</t>
-        </is>
-      </c>
+      <c r="A6" s="15" t="n"/>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="17" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="17" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
+      <c r="A31" s="15" t="n"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="17" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
+      <c r="A32" s="15" t="n"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="17" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="11" t="n"/>
-      <c r="G34" s="11" t="n"/>
+      <c r="A34" s="15" t="n"/>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
+      <c r="A35" s="15" t="n"/>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n"/>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="11" t="n"/>
-      <c r="G36" s="11" t="n"/>
+      <c r="A36" s="15" t="n"/>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
+      <c r="A37" s="15" t="n"/>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="17" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n"/>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="11" t="n"/>
-      <c r="G38" s="11" t="n"/>
+      <c r="A38" s="15" t="n"/>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n"/>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
-      <c r="G39" s="11" t="n"/>
+      <c r="A39" s="15" t="n"/>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n"/>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
-      <c r="G40" s="11" t="n"/>
+      <c r="A40" s="15" t="n"/>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n"/>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
+      <c r="A41" s="15" t="n"/>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
-      <c r="G42" s="11" t="n"/>
+      <c r="A42" s="15" t="n"/>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="17" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="n"/>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="15" t="n"/>
+      <c r="G43" s="17" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="n"/>
+      <c r="B44" s="15" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A7:G7"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="A8:A42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: cash, sales, delivery, customer, team" type="list">
+    <dataValidation sqref="A5:A44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: cash, sales, delivery, customer, team" promptTitle="Pick from the list" prompt="One winning metric gets picked per category" type="list">
       <formula1>"cash,sales,delivery,customer,team"</formula1>
     </dataValidation>
-    <dataValidation sqref="E8:E42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: higher_better, lower_better" type="list">
+    <dataValidation sqref="E5:E44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: higher_better, lower_better" promptTitle="Pick from the list" prompt="Is more of this good, or less?" type="list">
       <formula1>"higher_better,lower_better"</formula1>
     </dataValidation>
-    <dataValidation sqref="F8:F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: yes, no" type="list">
+    <dataValidation sqref="F5:F44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: yes, no" promptTitle="Pick from the list" prompt="Does this move before problems show elsewhere?" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="G8:G42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="G5:G44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." promptTitle="Rate 1 to 5" prompt="How directly this reflects business health" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
